--- a/Template_PRJ301_AI_Usage_Report_Template 10.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template 10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\COLLEGE\FALL26\PRJ201\aita-plagiarism-detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{076E364D-431E-4896-9CA8-0C0159D13083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E232C902-5BE0-44F5-B6B3-79767205A716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="89">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -269,6 +269,30 @@
   </si>
   <si>
     <t>AI failed to deeply understand the project's specific "academic market" logic and point-payment mechanism, resulting in a generic schema that required manual adjustments.</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find the actors may have in the system and see what usecases is appropriate in the system, Also generated SRS (Specification requi  file </t>
+  </si>
+  <si>
+    <t>Proposed a structure of 5 actor participate in the system (Student, lecture, systemadministrator, AI Similarity Engine and Acaedmic council) with some of use case  for each actor, it also give a SRS document about 11 pages.</t>
+  </si>
+  <si>
+    <t>Removed 2 secondary actors (AI Similarity Engine and Conference Council) and replace it with 2 new actor are External AI Service and AITA Submisson Portal acording to context of the system. (This is just my subjective opinion - chủ quan).</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1zzjKhSxxiEcWQbvnrOPi1hP_8b1GvXZD?usp=sharing</t>
+  </si>
+  <si>
+    <t>3 actors integrated in system finalized ver 1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although give specific context but AI still not fully understand the system and have some wrong external resulting identify wrong actors in the system. Also the SRS document pernamently still not haven't detected error but still need to follow up. </t>
   </si>
 </sst>
 </file>
@@ -356,7 +380,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -403,12 +427,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -437,19 +489,37 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -756,108 +826,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="14">
         <v>7</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
@@ -874,7 +944,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -887,7 +957,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -900,7 +970,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -913,7 +983,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>4</v>
       </c>
@@ -926,7 +996,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>5</v>
       </c>
@@ -957,22 +1027,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" customWidth="1"/>
+    <col min="7" max="7" width="24.86328125" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="61.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
@@ -1004,7 +1074,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="68.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1023,7 +1093,7 @@
       <c r="F2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="10" t="s">
         <v>73</v>
       </c>
       <c r="H2" s="6" t="s">
@@ -1036,36 +1106,68 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+    <row r="3" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="17">
         <v>4</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="18" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="123" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="20">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="20">
+        <v>1</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1080,7 +1182,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1094,7 +1196,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
@@ -1126,7 +1228,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1158,7 +1260,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1198,13 +1300,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>44</v>
       </c>
@@ -1212,7 +1314,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
@@ -1220,7 +1322,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>18</v>
       </c>
@@ -1228,7 +1330,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
@@ -1236,7 +1338,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>20</v>
       </c>
@@ -1244,7 +1346,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
         <v>21</v>
       </c>
@@ -1252,7 +1354,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
         <v>22</v>
       </c>
@@ -1260,7 +1362,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A8" s="8" t="s">
         <v>23</v>
       </c>
@@ -1268,7 +1370,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
         <v>24</v>
       </c>
@@ -1276,7 +1378,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" s="8" t="s">
         <v>25</v>
       </c>
@@ -1284,7 +1386,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
         <v>26</v>
       </c>

--- a/Template_PRJ301_AI_Usage_Report_Template 10.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template 10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\COLLEGE\FALL26\PRJ201\aita-plagiarism-detection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\aita-plagiarism-detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E232C902-5BE0-44F5-B6B3-79767205A716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5710EFE2-6F75-4488-A575-FA605D745580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -43,12 +43,21 @@
     <t>Class Code</t>
   </si>
   <si>
+    <t>SE20C</t>
+  </si>
+  <si>
     <t>Semester</t>
   </si>
   <si>
+    <t xml:space="preserve"> Fall 2026</t>
+  </si>
+  <si>
     <t>Lecturer Name</t>
   </si>
   <si>
+    <t>Nguyễn Hoài Nhi</t>
+  </si>
+  <si>
     <t>Group Code</t>
   </si>
   <si>
@@ -76,6 +85,33 @@
     <t>AI Tool Usaged</t>
   </si>
   <si>
+    <t>Qe200105</t>
+  </si>
+  <si>
+    <t>Nguyễn Trần Anh Kiệt</t>
+  </si>
+  <si>
+    <t>Qe200062</t>
+  </si>
+  <si>
+    <t>Đinh Vũ Phương Khánh</t>
+  </si>
+  <si>
+    <t>Qe200133</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Tiến</t>
+  </si>
+  <si>
+    <t>Qe2000141</t>
+  </si>
+  <si>
+    <t>Trần Văn Phúc</t>
+  </si>
+  <si>
+    <t>Qe200069</t>
+  </si>
+  <si>
     <t>No.</t>
   </si>
   <si>
@@ -106,10 +142,67 @@
     <t>Risks / Limitations Observed</t>
   </si>
   <si>
-    <t>ChatGPT</t>
+    <t>Requirement &amp; Foundation</t>
+  </si>
+  <si>
+    <t>Research Apache Tomcat and generate setup guide for team members</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>Generated a comprehensive guide explaining Tomcat concepts, directory structure, port conflict resolution, and IDE integration steps.</t>
+  </si>
+  <si>
+    <t>Reviewed technical accuracy, formatted the output into a Word document, and verified that the IntelliJ/Eclipse setup steps match the team's current environment.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1LGPjT0u5jygjKFlMjMxu0EP-gPwl7bnJ?usp=drive_link</t>
+  </si>
+  <si>
+    <t>1 technical guide document (5 sections)</t>
+  </si>
+  <si>
+    <t>AI provided slightly generic IDE instructions; required manual verification to ensure it matches the latest IntelliJ Ultimate UI.</t>
   </si>
   <si>
     <t>Design</t>
+  </si>
+  <si>
+    <t>Build Database schema (ERD) for the appeal handling and peer-review flow</t>
+  </si>
+  <si>
+    <t>Proposed a structure of 6 database tables (User, Course, Appeal_Ticket, Peer_Review, Sandbox_Log) with basic primary and foreign keys.</t>
+  </si>
+  <si>
+    <t>Redesigned the User table to add the correction_points field and adjusted the Peer_Review table to correctly accommodate the team's circular cross-grading logic (G1 -&gt; G2 -&gt; G3).</t>
+  </si>
+  <si>
+    <t>5 finalized database entities</t>
+  </si>
+  <si>
+    <t>AI failed to deeply understand the project's specific "academic market" logic and point-payment mechanism, resulting in a generic schema that required manual adjustments.</t>
+  </si>
+  <si>
+    <t>Implementation &amp; Foundation</t>
+  </si>
+  <si>
+    <t>Research JDBC connection flow and configure DBContext.java for SQL Server connectivity</t>
+  </si>
+  <si>
+    <t>Provided a standard Java JDBC connection template using DriverManager and basic connection URL structure.</t>
+  </si>
+  <si>
+    <t>Added mssql-jdbc dependency, fixed SSL handshake error by appending ';encrypt=true;trustServerCertificate=true' to the connection URL, and wrote a main() test method to confirm database connectivity.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CTGenIGc7blsUzn6XzbH_fcTr02xLfsT/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>1 DBContext class, 1 successful test connection log</t>
+  </si>
+  <si>
+    <t>AI provided generic JDBC syntax that omitted modern SQL Server SSL requirements, causing an initial connection crash.</t>
   </si>
   <si>
     <t>&lt;&lt;sample data&gt;&gt;
@@ -141,6 +234,9 @@
   </si>
   <si>
     <t>Test case generation for login &amp; submission upload</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
   </si>
   <si>
     <t>12 draft test cases (positive/negative)</t>
@@ -196,103 +292,52 @@
     <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
   </si>
   <si>
-    <t>Qe200105</t>
-  </si>
-  <si>
-    <t>Qe200062</t>
-  </si>
-  <si>
-    <t>Qe200133</t>
-  </si>
-  <si>
-    <t>Qe2000141</t>
-  </si>
-  <si>
-    <t>Qe200069</t>
-  </si>
-  <si>
-    <t>Nguyễn Trần Anh Kiệt</t>
-  </si>
-  <si>
-    <t>Đinh Vũ Phương Khánh</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Tiến</t>
-  </si>
-  <si>
-    <t>Trần Văn Phúc</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoài Nhi</t>
-  </si>
-  <si>
-    <t>SE20C</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fall 2026</t>
-  </si>
-  <si>
-    <t>Requirement &amp; Foundation</t>
-  </si>
-  <si>
-    <t>Research Apache Tomcat and generate setup guide for team members</t>
-  </si>
-  <si>
-    <t>Gemini</t>
-  </si>
-  <si>
-    <t>Generated a comprehensive guide explaining Tomcat concepts, directory structure, port conflict resolution, and IDE integration steps.</t>
-  </si>
-  <si>
-    <t>Reviewed technical accuracy, formatted the output into a Word document, and verified that the IntelliJ/Eclipse setup steps match the team's current environment.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1LGPjT0u5jygjKFlMjMxu0EP-gPwl7bnJ?usp=drive_link</t>
-  </si>
-  <si>
-    <t>1 technical guide document (5 sections)</t>
-  </si>
-  <si>
-    <t>AI provided slightly generic IDE instructions; required manual verification to ensure it matches the latest IntelliJ Ultimate UI.</t>
-  </si>
-  <si>
-    <t>Build Database schema (ERD) for the appeal handling and peer-review flow</t>
-  </si>
-  <si>
-    <t>Proposed a structure of 6 database tables (User, Course, Appeal_Ticket, Peer_Review, Sandbox_Log) with basic primary and foreign keys.</t>
-  </si>
-  <si>
-    <t>Redesigned the User table to add the correction_points field and adjusted the Peer_Review table to correctly accommodate the team's circular cross-grading logic (G1 -&gt; G2 -&gt; G3).</t>
-  </si>
-  <si>
-    <t>5 finalized database entities</t>
-  </si>
-  <si>
-    <t>AI failed to deeply understand the project's specific "academic market" logic and point-payment mechanism, resulting in a generic schema that required manual adjustments.</t>
-  </si>
-  <si>
-    <t>Requirement</t>
-  </si>
-  <si>
-    <t>Claude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find the actors may have in the system and see what usecases is appropriate in the system, Also generated SRS (Specification requi  file </t>
-  </si>
-  <si>
-    <t>Proposed a structure of 5 actor participate in the system (Student, lecture, systemadministrator, AI Similarity Engine and Acaedmic council) with some of use case  for each actor, it also give a SRS document about 11 pages.</t>
-  </si>
-  <si>
-    <t>Removed 2 secondary actors (AI Similarity Engine and Conference Council) and replace it with 2 new actor are External AI Service and AITA Submisson Portal acording to context of the system. (This is just my subjective opinion - chủ quan).</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1zzjKhSxxiEcWQbvnrOPi1hP_8b1GvXZD?usp=sharing</t>
-  </si>
-  <si>
-    <t>3 actors integrated in system finalized ver 1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Although give specific context but AI still not fully understand the system and have some wrong external resulting identify wrong actors in the system. Also the SRS document pernamently still not haven't detected error but still need to follow up. </t>
+    <t>ERD Entity &amp; Attribute Analysis for AITA AI Plagiarism &amp; Code Similarity Detection</t>
+  </si>
+  <si>
+    <t>Identified 6 core entities: USERS, COURSES, ASSIGNMENTS, SUBMISSIONS, PLAGIARISM_REPORTS and MATCHING_BLOCKS; summarized their main attributes and purposes.</t>
+  </si>
+  <si>
+    <t>Reviewed the proposed entities against the AITA system scope and retained only entities directly supporting course, assignment, submission and plagiarism/code-similarity analysis.</t>
+  </si>
+  <si>
+    <t>6 entities analyzed</t>
+  </si>
+  <si>
+    <t>AI may propose entities or attributes beyond the stated project scope.</t>
+  </si>
+  <si>
+    <t>PK/FK and Relationship Analysis</t>
+  </si>
+  <si>
+    <t>Analyzed primary keys, foreign keys and cardinalities for the 6 entities; identified 8 relationships including the two submission references in PLAGIARISM_REPORTS.</t>
+  </si>
+  <si>
+    <t>Checked each FK against its referenced table and verified 1:N relationships. Flagged business rules that role values must be respected for instructor_id and student_id.</t>
+  </si>
+  <si>
+    <t>6 PKs; 8 relationships; 8 FK fields/references analyzed</t>
+  </si>
+  <si>
+    <t>ERD relationships alone cannot enforce that referenced USERS have the correct role without additional constraints/application validation.</t>
+  </si>
+  <si>
+    <t>ERD Validation &amp; Revision</t>
+  </si>
+  <si>
+    <t>Reviewed the complete AITA ERD and identified design considerations for submission comparison, plagiarism reports and matching code blocks.</t>
+  </si>
+  <si>
+    <t>Validated the ERD against the AITA workflow and noted improvements such as allowing a plagiarism report to contain zero or more matching blocks and avoiding MD5 for password hashing in a real system.</t>
+  </si>
+  <si>
+    <t>6 entities; 8 relationships; 1 ERD revision checklist</t>
+  </si>
+  <si>
+    <t>Some security/business rules cannot be fully represented by ERD cardinality alone and require database constraints or application logic.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mxpQdZA5OAASAkW3LTrixKhtVqmWBOi_/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -380,7 +425,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -427,40 +472,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB7B7B7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB7B7B7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB7B7B7"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -492,35 +509,19 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -826,193 +827,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="12">
         <v>7</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="14">
-        <v>7</v>
-      </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
@@ -1020,6 +1019,8 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1027,153 +1028,249 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="24.86328125" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="61.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="68.45" customHeight="1" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="68.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="17">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="B3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="17">
+      <c r="E4" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="5">
         <v>4</v>
       </c>
-      <c r="J3" s="18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="123" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="20">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="20">
-        <v>1</v>
-      </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="5">
+        <v>5</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>88</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="5">
+        <v>4</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="5">
+        <v>5</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{DCB8BA9F-68F6-4834-9DE4-9504A5A77877}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{7AB302C7-1A33-42D7-ACF8-2076703EEAEA}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1182,7 +1279,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1196,100 +1293,100 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="38.25" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1300,98 +1397,98 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="38.25" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="25.5" x14ac:dyDescent="0.45">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Template_PRJ301_AI_Usage_Report_Template 10.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template 10.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\aita-plagiarism-detection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phucv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5710EFE2-6F75-4488-A575-FA605D745580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9204" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="118">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -338,12 +337,54 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1mxpQdZA5OAASAkW3LTrixKhtVqmWBOi_/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>gemini</t>
+  </si>
+  <si>
+    <t>Requirement &amp; Analysis</t>
+  </si>
+  <si>
+    <t>Define AST and Fingerprinting Algorithm Architecture for Code Plagiarism Detection</t>
+  </si>
+  <si>
+    <t>Generated an architectural blueprint comparing token-based hashing (Winnowing algorithm) vs. Abstract Syntax Tree (AST) structure comparison for Java code</t>
+  </si>
+  <si>
+    <t>Evaluated complexity and feasibility in a Java Servlet environment. Selected AST parsing via JavaParser for structure analysis combined with SHA-256 code hashing for quick duplicate detection before triggering deep similarity analysis</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YXc5Oupa8NXSv2F0QathzKjLAbA7or3h/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>1 architectural proposal (2 detection strategies analyzed)</t>
+  </si>
+  <si>
+    <t>AI initially suggested heavy Python-based NLP models which would break the pure Java Web / Servlet environment constraint; required manual filtering for Java-native libraries</t>
+  </si>
+  <si>
+    <t>Design &amp; Prototyping</t>
+  </si>
+  <si>
+    <t>Draft System Use Case Diagram and Sequence Flow for Plagiarism Scan &amp; Reporting</t>
+  </si>
+  <si>
+    <t>Produced a Use Case breakdown and PlantUML sequence diagram for submission intake, background AST parsing, similarity matrix generation, and instructor report view.</t>
+  </si>
+  <si>
+    <t>Refined actor boundaries: separated automatic background scan from Instructor manual re-run action, and integrated session authentication checks into the servlet request pipeline.</t>
+  </si>
+  <si>
+    <t>1 Use Case diagram draft, 1 PlantUML sequence script</t>
+  </si>
+  <si>
+    <t>AI omitted asynchronous processing limits, so manual intervention was needed to specify how long-running plagiarism checks interact with Servlet HTTP timeout limits.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -393,7 +434,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -422,6 +463,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -477,7 +524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -512,16 +559,29 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -825,16 +885,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:5" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13"/>
@@ -842,85 +902,85 @@
       <c r="D1" s="13"/>
       <c r="E1" s="14"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="14"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="15" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="14"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
       <c r="E5" s="14"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="14"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="15" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="15">
         <v>7</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="14"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="15" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="14"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="13"/>
@@ -928,7 +988,7 @@
       <c r="D11" s="13"/>
       <c r="E11" s="14"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -945,7 +1005,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -958,7 +1018,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -971,7 +1031,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -984,7 +1044,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>4</v>
       </c>
@@ -995,9 +1055,11 @@
         <v>27</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>5</v>
       </c>
@@ -1012,6 +1074,8 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
@@ -1019,31 +1083,29 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="24.85546875" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
@@ -1075,7 +1137,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="68.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1107,7 +1169,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1139,7 +1201,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1171,7 +1233,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1203,7 +1265,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1235,7 +1297,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1267,19 +1329,85 @@
         <v>59</v>
       </c>
     </row>
+    <row r="8" spans="1:10" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
+        <v>7</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8" s="18">
+        <v>5</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="20">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="20">
+        <v>4</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="G2" r:id="rId1"/>
+    <hyperlink ref="G3" r:id="rId2"/>
+    <hyperlink ref="G8" r:id="rId3"/>
+    <hyperlink ref="G9" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1293,7 +1421,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
@@ -1325,7 +1453,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1357,7 +1485,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1395,15 +1523,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>76</v>
       </c>
@@ -1411,7 +1539,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>29</v>
       </c>
@@ -1419,7 +1547,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>30</v>
       </c>
@@ -1427,7 +1555,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>31</v>
       </c>
@@ -1435,7 +1563,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>32</v>
       </c>
@@ -1443,7 +1571,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>33</v>
       </c>
@@ -1451,7 +1579,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>34</v>
       </c>
@@ -1459,7 +1587,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>35</v>
       </c>
@@ -1467,7 +1595,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>36</v>
       </c>
@@ -1475,7 +1603,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
@@ -1483,7 +1611,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>38</v>
       </c>

--- a/Template_PRJ301_AI_Usage_Report_Template 10.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template 10.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phucv\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\COLLEGE\FALL26\PRJ201\aita-plagiarism-detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9FDE2B-BFC6-4385-BB99-BD34D6713374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9204" activeTab="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="126">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -379,12 +380,36 @@
   </si>
   <si>
     <t>AI omitted asynchronous processing limits, so manual intervention was needed to specify how long-running plagiarism checks interact with Servlet HTTP timeout limits.</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find the actors may have in the system and see what usecases is appropriate in the system, Also generated SRS (Specification requi  file </t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>Proposed a structure of 5 actor participate in the system (Student, lecture, systemadministrator, AI Similarity Engine and Acaedmic council) with some of use case  for each actor, it also give a SRS document about 11 pages.</t>
+  </si>
+  <si>
+    <t>Removed 2 secondary actors (AI Similarity Engine and Conference Council) and replace it with 2 new actor are External AI Service and AITA Submisson Portal acording to context of the system. (This is just my subjective opinion - chủ quan).</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1zzjKhSxxiEcWQbvnrOPi1hP_8b1GvXZD?usp=sharing</t>
+  </si>
+  <si>
+    <t>3 actors integrated in system finalized ver 1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although give specific context but AI still not fully understand the system and have some wrong external resulting identify wrong actors in the system. Also the SRS document pernamently still not haven't detected error but still need to follow up. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -472,7 +497,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -519,12 +544,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -559,30 +612,31 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -885,110 +939,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="14"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="15"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="15"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="16">
         <v>7</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -1005,7 +1059,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -1018,7 +1072,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -1031,7 +1085,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -1044,7 +1098,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>4</v>
       </c>
@@ -1059,7 +1113,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>5</v>
       </c>
@@ -1089,9 +1143,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" customWidth="1"/>
@@ -1099,13 +1153,13 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" customWidth="1"/>
+    <col min="7" max="7" width="24.86328125" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="61.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
@@ -1137,7 +1191,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="68.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1169,7 +1223,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1201,7 +1255,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1233,7 +1287,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1265,7 +1319,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1297,7 +1351,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1329,85 +1383,117 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+    <row r="8" spans="1:10" ht="102" x14ac:dyDescent="0.45">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="5">
         <v>5</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="20">
+    <row r="9" spans="1:10" ht="89.25" x14ac:dyDescent="0.45">
+      <c r="A9" s="18">
         <v>8</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="18">
         <v>4</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="19" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="114.75" x14ac:dyDescent="0.45">
+      <c r="A10" s="20">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="I10" s="20">
+        <v>1</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1"/>
-    <hyperlink ref="G3" r:id="rId2"/>
-    <hyperlink ref="G8" r:id="rId3"/>
-    <hyperlink ref="G9" r:id="rId4"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="G8" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="G9" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1421,7 +1507,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
@@ -1453,7 +1539,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1485,7 +1571,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="26.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1523,15 +1609,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>76</v>
       </c>
@@ -1539,7 +1625,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="s">
         <v>29</v>
       </c>
@@ -1547,7 +1633,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>30</v>
       </c>
@@ -1555,7 +1641,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>31</v>
       </c>
@@ -1563,7 +1649,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>32</v>
       </c>
@@ -1571,7 +1657,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
         <v>33</v>
       </c>
@@ -1579,7 +1665,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
         <v>34</v>
       </c>
@@ -1587,7 +1673,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="39.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="8" t="s">
         <v>35</v>
       </c>
@@ -1595,7 +1681,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
         <v>36</v>
       </c>
@@ -1603,7 +1689,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
@@ -1611,7 +1697,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
         <v>38</v>
       </c>
